--- a/outputs/question-bank-596-text-20260908/银行从业初级银行管理_章节练习_题目整理.xlsx
+++ b/outputs/question-bank-596-text-20260908/银行从业初级银行管理_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R6eb8bab9ca064b12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R5f958b3bfa4c4f58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R7d0e0ccc47b74ac0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rd9db74c2b678457c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R61be0c57c01c4018"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rab9d3b5dbfaf42d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36786,7 +36786,7 @@
         <x:v>https://wx.233.com/center/study/tiku/chapter?domain=ccbp&amp;subjectId=1247&amp;chapterType=1</x:v>
       </x:c>
     </x:row>
-    <x:row r="596" ht="92" customHeight="1">
+    <x:row r="596" ht="157.5" customHeight="1">
       <x:c r="A596" s="8" t="n">
         <x:v>595</x:v>
       </x:c>
